--- a/data/products/p-gsb-001/work/views/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/views/Clear-Budget.xlsx
@@ -13187,7 +13187,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>

--- a/data/products/p-gsb-001/work/views/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/views/Clear-Budget.xlsx
@@ -28,10 +28,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Savings goals" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="Year">'Setup'!$C$6</definedName>
+    <definedName name="BudgetYear">'Setup'!$C$6</definedName>
     <definedName name="Categories">'Setup'!$E$10:$E$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Start here'!$B$2:$E$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Dashboard'!$B$2:$I$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Dashboard'!$B$2:$I$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Setup'!$B$2:$G$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'January'!$B$2:$L$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'February'!$B$2:$L$30</definedName>
@@ -46,7 +46,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="13">'November'!$B$2:$L$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'December'!$B$2:$L$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'Bills'!$B$2:$Q$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'Paycheck plan'!$B$2:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'Paycheck plan'!$B$2:$J$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'Debt payoff'!$B$2:$J$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'Savings goals'!$B$2:$H$12</definedName>
   </definedNames>
@@ -392,9 +392,14 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1300" b="1">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1300" b="1">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
               <a:t>Income and spending by month</a:t>
             </a:r>
           </a:p>
@@ -477,6 +482,20 @@
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -490,11 +509,39 @@
         <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr/>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -511,9 +558,14 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1300" b="1">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1300" b="1">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
               <a:t>Where the money went</a:t>
             </a:r>
           </a:p>
@@ -592,6 +644,20 @@
           </val>
         </ser>
         <dLbls>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="900" b="0">
+                  <a:latin typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+              <a:endParaRPr/>
+            </a:p>
+          </txPr>
           <showVal val="0"/>
           <showCatName val="0"/>
           <showSerName val="0"/>
@@ -603,6 +669,20 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr/>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1247,7 +1327,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="20" customHeight="1">
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Check</t>
@@ -1665,7 +1745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1755,7 +1835,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -1791,7 +1871,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -1806,7 +1886,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -1821,7 +1901,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -1836,13 +1916,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -1874,7 +1954,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -1904,7 +1984,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -1934,7 +2014,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -1964,7 +2044,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -1994,7 +2074,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -2024,7 +2104,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -2054,7 +2134,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -2084,7 +2164,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -2114,7 +2194,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -2144,7 +2224,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -2174,7 +2254,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -2204,7 +2284,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -2234,7 +2314,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -2264,7 +2344,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -2294,7 +2374,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -2324,7 +2404,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -2354,7 +2434,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -2384,7 +2464,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -2414,7 +2494,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -2444,7 +2524,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -2474,7 +2554,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -2504,7 +2584,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -2534,7 +2614,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -2564,7 +2644,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -2594,7 +2674,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -2624,7 +2704,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -2654,7 +2734,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -2684,7 +2764,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -2714,7 +2794,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -2744,7 +2824,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -2774,275 +2854,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -3089,7 +3176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3179,7 +3266,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -3215,7 +3302,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -3230,7 +3317,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -3245,7 +3332,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -3260,13 +3347,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -3298,7 +3385,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -3328,7 +3415,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -3358,7 +3445,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -3388,7 +3475,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -3418,7 +3505,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -3448,7 +3535,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -3478,7 +3565,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -3508,7 +3595,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -3538,7 +3625,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -3568,7 +3655,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -3598,7 +3685,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -3628,7 +3715,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -3658,7 +3745,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -3688,7 +3775,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -3718,7 +3805,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -3748,7 +3835,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -3778,7 +3865,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -3808,7 +3895,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -3838,7 +3925,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -3868,7 +3955,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -3898,7 +3985,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -3928,7 +4015,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -3958,7 +4045,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -3988,7 +4075,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -4018,7 +4105,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -4048,7 +4135,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -4078,7 +4165,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -4108,7 +4195,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -4138,7 +4225,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -4168,7 +4255,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -4198,275 +4285,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -4513,7 +4607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4603,7 +4697,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -4639,7 +4733,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -4654,7 +4748,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -4669,7 +4763,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -4684,13 +4778,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -4722,7 +4816,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -4752,7 +4846,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -4782,7 +4876,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -4812,7 +4906,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -4842,7 +4936,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -4872,7 +4966,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -4902,7 +4996,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -4932,7 +5026,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -4962,7 +5056,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -4992,7 +5086,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -5022,7 +5116,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -5052,7 +5146,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -5082,7 +5176,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -5112,7 +5206,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -5142,7 +5236,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -5172,7 +5266,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -5202,7 +5296,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -5232,7 +5326,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -5262,7 +5356,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -5292,7 +5386,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -5322,7 +5416,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -5352,7 +5446,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -5382,7 +5476,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -5412,7 +5506,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -5442,7 +5536,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -5472,7 +5566,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -5502,7 +5596,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -5532,7 +5626,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -5562,7 +5656,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -5592,7 +5686,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -5622,275 +5716,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -5937,7 +6038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6027,7 +6128,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -6063,7 +6164,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -6078,7 +6179,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -6093,7 +6194,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -6108,13 +6209,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -6146,7 +6247,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -6176,7 +6277,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -6206,7 +6307,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -6236,7 +6337,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -6266,7 +6367,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -6296,7 +6397,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -6326,7 +6427,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -6356,7 +6457,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -6386,7 +6487,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -6416,7 +6517,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -6446,7 +6547,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -6476,7 +6577,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -6506,7 +6607,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -6536,7 +6637,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -6566,7 +6667,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -6596,7 +6697,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -6626,7 +6727,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -6656,7 +6757,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -6686,7 +6787,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -6716,7 +6817,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -6746,7 +6847,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -6776,7 +6877,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -6806,7 +6907,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -6836,7 +6937,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -6866,7 +6967,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -6896,7 +6997,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -6926,7 +7027,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -6956,7 +7057,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -6986,7 +7087,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -7016,7 +7117,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -7046,275 +7147,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -7361,7 +7469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7451,7 +7559,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -7487,7 +7595,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -7502,7 +7610,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -7517,7 +7625,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -7532,13 +7640,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -7570,7 +7678,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -7600,7 +7708,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -7630,7 +7738,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -7660,7 +7768,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -7690,7 +7798,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -7720,7 +7828,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -7750,7 +7858,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -7780,7 +7888,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -7810,7 +7918,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -7840,7 +7948,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -7870,7 +7978,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -7900,7 +8008,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -7930,7 +8038,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -7960,7 +8068,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -7990,7 +8098,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -8020,7 +8128,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -8050,7 +8158,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -8080,7 +8188,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -8110,7 +8218,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -8140,7 +8248,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -8170,7 +8278,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -8200,7 +8308,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -8230,7 +8338,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -8260,7 +8368,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -8290,7 +8398,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -8320,7 +8428,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -8350,7 +8458,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -8380,7 +8488,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -8410,7 +8518,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -8440,7 +8548,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -8470,275 +8578,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -8785,7 +8900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8875,7 +8990,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -8911,7 +9026,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -8926,7 +9041,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -8941,7 +9056,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -8956,13 +9071,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -8994,7 +9109,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -9024,7 +9139,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -9054,7 +9169,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -9084,7 +9199,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -9114,7 +9229,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -9144,7 +9259,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -9174,7 +9289,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -9204,7 +9319,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -9234,7 +9349,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -9264,7 +9379,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -9294,7 +9409,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -9324,7 +9439,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -9354,7 +9469,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -9384,7 +9499,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -9414,7 +9529,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -9444,7 +9559,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -9474,7 +9589,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -9504,7 +9619,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -9534,7 +9649,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -9564,7 +9679,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -9594,7 +9709,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -9624,7 +9739,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -9654,7 +9769,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -9684,7 +9799,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -9714,7 +9829,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -9744,7 +9859,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -9774,7 +9889,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -9804,7 +9919,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -9834,7 +9949,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -9864,7 +9979,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -9894,275 +10009,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -10299,7 +10421,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Bill</t>
@@ -10991,7 +11113,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Paid weekly or every two weeks? See which bills each paycheck covers. Paid monthly? Skip this tab.</t>
+          <t>Paid weekly, every two weeks or twice a month? See which bills each paycheck covers. Paid monthly? Skip this tab.</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11166,7 @@
         </is>
       </c>
       <c r="C6" s="33">
-        <f>DATE(Year,1,1)+MOD(6-WEEKDAY(DATE(Year,1,1)),7)</f>
+        <f>DATE(BudgetYear,1,1)+MOD(6-WEEKDAY(DATE(BudgetYear,1,1)),7)</f>
         <v/>
       </c>
     </row>
@@ -11127,7 +11249,7 @@
     </row>
     <row r="12">
       <c r="B12" s="34">
-        <f>IF(F11="","",IF(F11&gt;DATE(Year,12,31),"",F11))</f>
+        <f>IF(F11="","",IF(F11&gt;DATE(BudgetYear,12,31),"",F11))</f>
         <v/>
       </c>
       <c r="C12" s="24">
@@ -11149,7 +11271,7 @@
     </row>
     <row r="13">
       <c r="B13" s="34">
-        <f>IF(F12="","",IF(F12&gt;DATE(Year,12,31),"",F12))</f>
+        <f>IF(F12="","",IF(F12&gt;DATE(BudgetYear,12,31),"",F12))</f>
         <v/>
       </c>
       <c r="C13" s="24">
@@ -11171,7 +11293,7 @@
     </row>
     <row r="14">
       <c r="B14" s="34">
-        <f>IF(F13="","",IF(F13&gt;DATE(Year,12,31),"",F13))</f>
+        <f>IF(F13="","",IF(F13&gt;DATE(BudgetYear,12,31),"",F13))</f>
         <v/>
       </c>
       <c r="C14" s="24">
@@ -11193,7 +11315,7 @@
     </row>
     <row r="15">
       <c r="B15" s="34">
-        <f>IF(F14="","",IF(F14&gt;DATE(Year,12,31),"",F14))</f>
+        <f>IF(F14="","",IF(F14&gt;DATE(BudgetYear,12,31),"",F14))</f>
         <v/>
       </c>
       <c r="C15" s="24">
@@ -11215,7 +11337,7 @@
     </row>
     <row r="16">
       <c r="B16" s="34">
-        <f>IF(F15="","",IF(F15&gt;DATE(Year,12,31),"",F15))</f>
+        <f>IF(F15="","",IF(F15&gt;DATE(BudgetYear,12,31),"",F15))</f>
         <v/>
       </c>
       <c r="C16" s="24">
@@ -11237,7 +11359,7 @@
     </row>
     <row r="17">
       <c r="B17" s="34">
-        <f>IF(F16="","",IF(F16&gt;DATE(Year,12,31),"",F16))</f>
+        <f>IF(F16="","",IF(F16&gt;DATE(BudgetYear,12,31),"",F16))</f>
         <v/>
       </c>
       <c r="C17" s="24">
@@ -11259,7 +11381,7 @@
     </row>
     <row r="18">
       <c r="B18" s="34">
-        <f>IF(F17="","",IF(F17&gt;DATE(Year,12,31),"",F17))</f>
+        <f>IF(F17="","",IF(F17&gt;DATE(BudgetYear,12,31),"",F17))</f>
         <v/>
       </c>
       <c r="C18" s="24">
@@ -11281,7 +11403,7 @@
     </row>
     <row r="19">
       <c r="B19" s="34">
-        <f>IF(F18="","",IF(F18&gt;DATE(Year,12,31),"",F18))</f>
+        <f>IF(F18="","",IF(F18&gt;DATE(BudgetYear,12,31),"",F18))</f>
         <v/>
       </c>
       <c r="C19" s="24">
@@ -11303,7 +11425,7 @@
     </row>
     <row r="20">
       <c r="B20" s="34">
-        <f>IF(F19="","",IF(F19&gt;DATE(Year,12,31),"",F19))</f>
+        <f>IF(F19="","",IF(F19&gt;DATE(BudgetYear,12,31),"",F19))</f>
         <v/>
       </c>
       <c r="C20" s="24">
@@ -11325,7 +11447,7 @@
     </row>
     <row r="21">
       <c r="B21" s="34">
-        <f>IF(F20="","",IF(F20&gt;DATE(Year,12,31),"",F20))</f>
+        <f>IF(F20="","",IF(F20&gt;DATE(BudgetYear,12,31),"",F20))</f>
         <v/>
       </c>
       <c r="C21" s="24">
@@ -11347,7 +11469,7 @@
     </row>
     <row r="22">
       <c r="B22" s="34">
-        <f>IF(F21="","",IF(F21&gt;DATE(Year,12,31),"",F21))</f>
+        <f>IF(F21="","",IF(F21&gt;DATE(BudgetYear,12,31),"",F21))</f>
         <v/>
       </c>
       <c r="C22" s="24">
@@ -11369,7 +11491,7 @@
     </row>
     <row r="23">
       <c r="B23" s="34">
-        <f>IF(F22="","",IF(F22&gt;DATE(Year,12,31),"",F22))</f>
+        <f>IF(F22="","",IF(F22&gt;DATE(BudgetYear,12,31),"",F22))</f>
         <v/>
       </c>
       <c r="C23" s="24">
@@ -11391,7 +11513,7 @@
     </row>
     <row r="24">
       <c r="B24" s="34">
-        <f>IF(F23="","",IF(F23&gt;DATE(Year,12,31),"",F23))</f>
+        <f>IF(F23="","",IF(F23&gt;DATE(BudgetYear,12,31),"",F23))</f>
         <v/>
       </c>
       <c r="C24" s="24">
@@ -11413,7 +11535,7 @@
     </row>
     <row r="25">
       <c r="B25" s="34">
-        <f>IF(F24="","",IF(F24&gt;DATE(Year,12,31),"",F24))</f>
+        <f>IF(F24="","",IF(F24&gt;DATE(BudgetYear,12,31),"",F24))</f>
         <v/>
       </c>
       <c r="C25" s="24">
@@ -11435,7 +11557,7 @@
     </row>
     <row r="26">
       <c r="B26" s="34">
-        <f>IF(F25="","",IF(F25&gt;DATE(Year,12,31),"",F25))</f>
+        <f>IF(F25="","",IF(F25&gt;DATE(BudgetYear,12,31),"",F25))</f>
         <v/>
       </c>
       <c r="C26" s="24">
@@ -11457,7 +11579,7 @@
     </row>
     <row r="27">
       <c r="B27" s="34">
-        <f>IF(F26="","",IF(F26&gt;DATE(Year,12,31),"",F26))</f>
+        <f>IF(F26="","",IF(F26&gt;DATE(BudgetYear,12,31),"",F26))</f>
         <v/>
       </c>
       <c r="C27" s="24">
@@ -11479,7 +11601,7 @@
     </row>
     <row r="28">
       <c r="B28" s="34">
-        <f>IF(F27="","",IF(F27&gt;DATE(Year,12,31),"",F27))</f>
+        <f>IF(F27="","",IF(F27&gt;DATE(BudgetYear,12,31),"",F27))</f>
         <v/>
       </c>
       <c r="C28" s="24">
@@ -11501,7 +11623,7 @@
     </row>
     <row r="29">
       <c r="B29" s="34">
-        <f>IF(F28="","",IF(F28&gt;DATE(Year,12,31),"",F28))</f>
+        <f>IF(F28="","",IF(F28&gt;DATE(BudgetYear,12,31),"",F28))</f>
         <v/>
       </c>
       <c r="C29" s="24">
@@ -11523,7 +11645,7 @@
     </row>
     <row r="30">
       <c r="B30" s="34">
-        <f>IF(F29="","",IF(F29&gt;DATE(Year,12,31),"",F29))</f>
+        <f>IF(F29="","",IF(F29&gt;DATE(BudgetYear,12,31),"",F29))</f>
         <v/>
       </c>
       <c r="C30" s="24">
@@ -11545,7 +11667,7 @@
     </row>
     <row r="31">
       <c r="B31" s="34">
-        <f>IF(F30="","",IF(F30&gt;DATE(Year,12,31),"",F30))</f>
+        <f>IF(F30="","",IF(F30&gt;DATE(BudgetYear,12,31),"",F30))</f>
         <v/>
       </c>
       <c r="C31" s="24">
@@ -11567,7 +11689,7 @@
     </row>
     <row r="32">
       <c r="B32" s="34">
-        <f>IF(F31="","",IF(F31&gt;DATE(Year,12,31),"",F31))</f>
+        <f>IF(F31="","",IF(F31&gt;DATE(BudgetYear,12,31),"",F31))</f>
         <v/>
       </c>
       <c r="C32" s="24">
@@ -11589,7 +11711,7 @@
     </row>
     <row r="33">
       <c r="B33" s="34">
-        <f>IF(F32="","",IF(F32&gt;DATE(Year,12,31),"",F32))</f>
+        <f>IF(F32="","",IF(F32&gt;DATE(BudgetYear,12,31),"",F32))</f>
         <v/>
       </c>
       <c r="C33" s="24">
@@ -11611,7 +11733,7 @@
     </row>
     <row r="34">
       <c r="B34" s="34">
-        <f>IF(F33="","",IF(F33&gt;DATE(Year,12,31),"",F33))</f>
+        <f>IF(F33="","",IF(F33&gt;DATE(BudgetYear,12,31),"",F33))</f>
         <v/>
       </c>
       <c r="C34" s="24">
@@ -11633,7 +11755,7 @@
     </row>
     <row r="35">
       <c r="B35" s="34">
-        <f>IF(F34="","",IF(F34&gt;DATE(Year,12,31),"",F34))</f>
+        <f>IF(F34="","",IF(F34&gt;DATE(BudgetYear,12,31),"",F34))</f>
         <v/>
       </c>
       <c r="C35" s="24">
@@ -11655,7 +11777,7 @@
     </row>
     <row r="36">
       <c r="B36" s="34">
-        <f>IF(F35="","",IF(F35&gt;DATE(Year,12,31),"",F35))</f>
+        <f>IF(F35="","",IF(F35&gt;DATE(BudgetYear,12,31),"",F35))</f>
         <v/>
       </c>
       <c r="C36" s="24">
@@ -11677,7 +11799,7 @@
     </row>
     <row r="37">
       <c r="B37" s="34">
-        <f>IF(F36="","",IF(F36&gt;DATE(Year,12,31),"",F36))</f>
+        <f>IF(F36="","",IF(F36&gt;DATE(BudgetYear,12,31),"",F36))</f>
         <v/>
       </c>
       <c r="C37" s="24">
@@ -11699,7 +11821,7 @@
     </row>
     <row r="38">
       <c r="B38" s="34">
-        <f>IF(F37="","",IF(F37&gt;DATE(Year,12,31),"",F37))</f>
+        <f>IF(F37="","",IF(F37&gt;DATE(BudgetYear,12,31),"",F37))</f>
         <v/>
       </c>
       <c r="C38" s="24">
@@ -11721,7 +11843,7 @@
     </row>
     <row r="39">
       <c r="B39" s="34">
-        <f>IF(F38="","",IF(F38&gt;DATE(Year,12,31),"",F38))</f>
+        <f>IF(F38="","",IF(F38&gt;DATE(BudgetYear,12,31),"",F38))</f>
         <v/>
       </c>
       <c r="C39" s="24">
@@ -11743,7 +11865,7 @@
     </row>
     <row r="40">
       <c r="B40" s="34">
-        <f>IF(F39="","",IF(F39&gt;DATE(Year,12,31),"",F39))</f>
+        <f>IF(F39="","",IF(F39&gt;DATE(BudgetYear,12,31),"",F39))</f>
         <v/>
       </c>
       <c r="C40" s="24">
@@ -11765,7 +11887,7 @@
     </row>
     <row r="41">
       <c r="B41" s="34">
-        <f>IF(F40="","",IF(F40&gt;DATE(Year,12,31),"",F40))</f>
+        <f>IF(F40="","",IF(F40&gt;DATE(BudgetYear,12,31),"",F40))</f>
         <v/>
       </c>
       <c r="C41" s="24">
@@ -11787,7 +11909,7 @@
     </row>
     <row r="42">
       <c r="B42" s="34">
-        <f>IF(F41="","",IF(F41&gt;DATE(Year,12,31),"",F41))</f>
+        <f>IF(F41="","",IF(F41&gt;DATE(BudgetYear,12,31),"",F41))</f>
         <v/>
       </c>
       <c r="C42" s="24">
@@ -11809,7 +11931,7 @@
     </row>
     <row r="43">
       <c r="B43" s="34">
-        <f>IF(F42="","",IF(F42&gt;DATE(Year,12,31),"",F42))</f>
+        <f>IF(F42="","",IF(F42&gt;DATE(BudgetYear,12,31),"",F42))</f>
         <v/>
       </c>
       <c r="C43" s="24">
@@ -11831,7 +11953,7 @@
     </row>
     <row r="44">
       <c r="B44" s="34">
-        <f>IF(F43="","",IF(F43&gt;DATE(Year,12,31),"",F43))</f>
+        <f>IF(F43="","",IF(F43&gt;DATE(BudgetYear,12,31),"",F43))</f>
         <v/>
       </c>
       <c r="C44" s="24">
@@ -11853,7 +11975,7 @@
     </row>
     <row r="45">
       <c r="B45" s="34">
-        <f>IF(F44="","",IF(F44&gt;DATE(Year,12,31),"",F44))</f>
+        <f>IF(F44="","",IF(F44&gt;DATE(BudgetYear,12,31),"",F44))</f>
         <v/>
       </c>
       <c r="C45" s="24">
@@ -11875,7 +11997,7 @@
     </row>
     <row r="46">
       <c r="B46" s="34">
-        <f>IF(F45="","",IF(F45&gt;DATE(Year,12,31),"",F45))</f>
+        <f>IF(F45="","",IF(F45&gt;DATE(BudgetYear,12,31),"",F45))</f>
         <v/>
       </c>
       <c r="C46" s="24">
@@ -11897,7 +12019,7 @@
     </row>
     <row r="47">
       <c r="B47" s="34">
-        <f>IF(F46="","",IF(F46&gt;DATE(Year,12,31),"",F46))</f>
+        <f>IF(F46="","",IF(F46&gt;DATE(BudgetYear,12,31),"",F46))</f>
         <v/>
       </c>
       <c r="C47" s="24">
@@ -11919,7 +12041,7 @@
     </row>
     <row r="48">
       <c r="B48" s="34">
-        <f>IF(F47="","",IF(F47&gt;DATE(Year,12,31),"",F47))</f>
+        <f>IF(F47="","",IF(F47&gt;DATE(BudgetYear,12,31),"",F47))</f>
         <v/>
       </c>
       <c r="C48" s="24">
@@ -11941,7 +12063,7 @@
     </row>
     <row r="49">
       <c r="B49" s="34">
-        <f>IF(F48="","",IF(F48&gt;DATE(Year,12,31),"",F48))</f>
+        <f>IF(F48="","",IF(F48&gt;DATE(BudgetYear,12,31),"",F48))</f>
         <v/>
       </c>
       <c r="C49" s="24">
@@ -11963,7 +12085,7 @@
     </row>
     <row r="50">
       <c r="B50" s="34">
-        <f>IF(F49="","",IF(F49&gt;DATE(Year,12,31),"",F49))</f>
+        <f>IF(F49="","",IF(F49&gt;DATE(BudgetYear,12,31),"",F49))</f>
         <v/>
       </c>
       <c r="C50" s="24">
@@ -11985,7 +12107,7 @@
     </row>
     <row r="51">
       <c r="B51" s="34">
-        <f>IF(F50="","",IF(F50&gt;DATE(Year,12,31),"",F50))</f>
+        <f>IF(F50="","",IF(F50&gt;DATE(BudgetYear,12,31),"",F50))</f>
         <v/>
       </c>
       <c r="C51" s="24">
@@ -12007,7 +12129,7 @@
     </row>
     <row r="52">
       <c r="B52" s="34">
-        <f>IF(F51="","",IF(F51&gt;DATE(Year,12,31),"",F51))</f>
+        <f>IF(F51="","",IF(F51&gt;DATE(BudgetYear,12,31),"",F51))</f>
         <v/>
       </c>
       <c r="C52" s="24">
@@ -12029,7 +12151,7 @@
     </row>
     <row r="53">
       <c r="B53" s="34">
-        <f>IF(F52="","",IF(F52&gt;DATE(Year,12,31),"",F52))</f>
+        <f>IF(F52="","",IF(F52&gt;DATE(BudgetYear,12,31),"",F52))</f>
         <v/>
       </c>
       <c r="C53" s="24">
@@ -12051,7 +12173,7 @@
     </row>
     <row r="54">
       <c r="B54" s="34">
-        <f>IF(F53="","",IF(F53&gt;DATE(Year,12,31),"",F53))</f>
+        <f>IF(F53="","",IF(F53&gt;DATE(BudgetYear,12,31),"",F53))</f>
         <v/>
       </c>
       <c r="C54" s="24">
@@ -12073,7 +12195,7 @@
     </row>
     <row r="55">
       <c r="B55" s="34">
-        <f>IF(F54="","",IF(F54&gt;DATE(Year,12,31),"",F54))</f>
+        <f>IF(F54="","",IF(F54&gt;DATE(BudgetYear,12,31),"",F54))</f>
         <v/>
       </c>
       <c r="C55" s="24">
@@ -12095,7 +12217,7 @@
     </row>
     <row r="56">
       <c r="B56" s="34">
-        <f>IF(F55="","",IF(F55&gt;DATE(Year,12,31),"",F55))</f>
+        <f>IF(F55="","",IF(F55&gt;DATE(BudgetYear,12,31),"",F55))</f>
         <v/>
       </c>
       <c r="C56" s="24">
@@ -12117,7 +12239,7 @@
     </row>
     <row r="57">
       <c r="B57" s="34">
-        <f>IF(F56="","",IF(F56&gt;DATE(Year,12,31),"",F56))</f>
+        <f>IF(F56="","",IF(F56&gt;DATE(BudgetYear,12,31),"",F56))</f>
         <v/>
       </c>
       <c r="C57" s="24">
@@ -12139,7 +12261,7 @@
     </row>
     <row r="58">
       <c r="B58" s="34">
-        <f>IF(F57="","",IF(F57&gt;DATE(Year,12,31),"",F57))</f>
+        <f>IF(F57="","",IF(F57&gt;DATE(BudgetYear,12,31),"",F57))</f>
         <v/>
       </c>
       <c r="C58" s="24">
@@ -12161,7 +12283,7 @@
     </row>
     <row r="59">
       <c r="B59" s="34">
-        <f>IF(F58="","",IF(F58&gt;DATE(Year,12,31),"",F58))</f>
+        <f>IF(F58="","",IF(F58&gt;DATE(BudgetYear,12,31),"",F58))</f>
         <v/>
       </c>
       <c r="C59" s="24">
@@ -12183,7 +12305,7 @@
     </row>
     <row r="60">
       <c r="B60" s="34">
-        <f>IF(F59="","",IF(F59&gt;DATE(Year,12,31),"",F59))</f>
+        <f>IF(F59="","",IF(F59&gt;DATE(BudgetYear,12,31),"",F59))</f>
         <v/>
       </c>
       <c r="C60" s="24">
@@ -12205,7 +12327,7 @@
     </row>
     <row r="61">
       <c r="B61" s="34">
-        <f>IF(F60="","",IF(F60&gt;DATE(Year,12,31),"",F60))</f>
+        <f>IF(F60="","",IF(F60&gt;DATE(BudgetYear,12,31),"",F60))</f>
         <v/>
       </c>
       <c r="C61" s="24">
@@ -12227,7 +12349,7 @@
     </row>
     <row r="62">
       <c r="B62" s="34">
-        <f>IF(F61="","",IF(F61&gt;DATE(Year,12,31),"",F61))</f>
+        <f>IF(F61="","",IF(F61&gt;DATE(BudgetYear,12,31),"",F61))</f>
         <v/>
       </c>
       <c r="C62" s="24">
@@ -12249,7 +12371,7 @@
     </row>
     <row r="63">
       <c r="B63" s="34">
-        <f>IF(F62="","",IF(F62&gt;DATE(Year,12,31),"",F62))</f>
+        <f>IF(F62="","",IF(F62&gt;DATE(BudgetYear,12,31),"",F62))</f>
         <v/>
       </c>
       <c r="C63" s="24">
@@ -12271,7 +12393,7 @@
     </row>
     <row r="64">
       <c r="B64" s="34">
-        <f>IF(F63="","",IF(F63&gt;DATE(Year,12,31),"",F63))</f>
+        <f>IF(F63="","",IF(F63&gt;DATE(BudgetYear,12,31),"",F63))</f>
         <v/>
       </c>
       <c r="C64" s="24">
@@ -12335,9 +12457,9 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -12443,7 +12565,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Debt</t>
@@ -12493,17 +12615,17 @@
     <row r="10">
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Credit card</t>
+          <t>Medical bill</t>
         </is>
       </c>
       <c r="C10" s="24" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0.2299</v>
+        <v>0</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F10" s="37">
         <f>IF(C10="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C10,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D10,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12529,17 +12651,17 @@
     <row r="11">
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Car loan</t>
+          <t>Credit card</t>
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>8200</v>
+        <v>2400</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.2299</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F11" s="37">
         <f>IF(C11="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C11,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D11,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12565,17 +12687,17 @@
     <row r="12">
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Student loan</t>
+          <t>Car loan</t>
         </is>
       </c>
       <c r="C12" s="24" t="n">
-        <v>14500</v>
+        <v>8200</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0.055</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F12" s="37">
         <f>IF(C12="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C12,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D12,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12599,10 +12721,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="24" t="n"/>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Student loan</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>14500</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>180</v>
+      </c>
       <c r="F13" s="37">
         <f>IF(C13="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C13,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D13,$C$10:$C$19,"&lt;&gt;")+1))</f>
         <v/>
@@ -12915,7 +13047,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Goal</t>
@@ -12946,7 +13078,11 @@
           <t>Save per month</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Progress bar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="15" t="inlineStr">
@@ -12968,7 +13104,7 @@
         <v>46722</v>
       </c>
       <c r="G7" s="20">
-        <f>IF(OR(C7="",F7=""),"",IF(D7&gt;=C7,"Reached",IF(((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C7-D7)/((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C7="",F7=""),"",IF(D7&gt;=C7,"Reached",IF(((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C7-D7)/MAX(1,((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H7" s="31">
@@ -12996,7 +13132,7 @@
         <v>46569</v>
       </c>
       <c r="G8" s="20">
-        <f>IF(OR(C8="",F8=""),"",IF(D8&gt;=C8,"Reached",IF(((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C8-D8)/((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C8="",F8=""),"",IF(D8&gt;=C8,"Reached",IF(((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C8-D8)/MAX(1,((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H8" s="31">
@@ -13024,7 +13160,7 @@
         <v>46631</v>
       </c>
       <c r="G9" s="20">
-        <f>IF(OR(C9="",F9=""),"",IF(D9&gt;=C9,"Reached",IF(((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C9-D9)/((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C9="",F9=""),"",IF(D9&gt;=C9,"Reached",IF(((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C9-D9)/MAX(1,((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H9" s="31">
@@ -13042,7 +13178,7 @@
       </c>
       <c r="F10" s="38" t="n"/>
       <c r="G10" s="20">
-        <f>IF(OR(C10="",F10=""),"",IF(D10&gt;=C10,"Reached",IF(((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C10-D10)/((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C10="",F10=""),"",IF(D10&gt;=C10,"Reached",IF(((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C10-D10)/MAX(1,((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H10" s="31">
@@ -13060,7 +13196,7 @@
       </c>
       <c r="F11" s="38" t="n"/>
       <c r="G11" s="20">
-        <f>IF(OR(C11="",F11=""),"",IF(D11&gt;=C11,"Reached",IF(((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C11-D11)/((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C11="",F11=""),"",IF(D11&gt;=C11,"Reached",IF(((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C11-D11)/MAX(1,((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H11" s="31">
@@ -13078,7 +13214,7 @@
       </c>
       <c r="F12" s="38" t="n"/>
       <c r="G12" s="20">
-        <f>IF(OR(C12="",F12=""),"",IF(D12&gt;=C12,"Reached",IF(((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C12-D12)/((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C12="",F12=""),"",IF(D12&gt;=C12,"Reached",IF(((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C12-D12)/MAX(1,((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H12" s="31">
@@ -13096,7 +13232,7 @@
       </c>
       <c r="F13" s="38" t="n"/>
       <c r="G13" s="20">
-        <f>IF(OR(C13="",F13=""),"",IF(D13&gt;=C13,"Reached",IF(((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C13-D13)/((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C13="",F13=""),"",IF(D13&gt;=C13,"Reached",IF(((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C13-D13)/MAX(1,((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H13" s="31">
@@ -13114,7 +13250,7 @@
       </c>
       <c r="F14" s="38" t="n"/>
       <c r="G14" s="20">
-        <f>IF(OR(C14="",F14=""),"",IF(D14&gt;=C14,"Reached",IF(((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C14-D14)/((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C14="",F14=""),"",IF(D14&gt;=C14,"Reached",IF(((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C14-D14)/MAX(1,((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H14" s="31">
@@ -13132,7 +13268,7 @@
       </c>
       <c r="F15" s="38" t="n"/>
       <c r="G15" s="20">
-        <f>IF(OR(C15="",F15=""),"",IF(D15&gt;=C15,"Reached",IF(((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C15-D15)/((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C15="",F15=""),"",IF(D15&gt;=C15,"Reached",IF(((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C15-D15)/MAX(1,((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H15" s="31">
@@ -13150,7 +13286,7 @@
       </c>
       <c r="F16" s="38" t="n"/>
       <c r="G16" s="20">
-        <f>IF(OR(C16="",F16=""),"",IF(D16&gt;=C16,"Reached",IF(((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C16-D16)/((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY())))))</f>
+        <f>IF(OR(C16="",F16=""),"",IF(D16&gt;=C16,"Reached",IF(((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C16-D16)/MAX(1,((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))))))</f>
         <v/>
       </c>
       <c r="H16" s="31">
@@ -13273,7 +13409,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Month</t>
@@ -13310,7 +13446,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="19" t="inlineStr">
         <is>
           <t>January</t>
@@ -13345,7 +13481,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>February</t>
@@ -13380,7 +13516,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
         <is>
           <t>March</t>
@@ -13415,7 +13551,7 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="19" t="inlineStr">
         <is>
           <t>April</t>
@@ -13450,7 +13586,7 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="19" t="inlineStr">
         <is>
           <t>May</t>
@@ -13485,7 +13621,7 @@
         <v/>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
         <is>
           <t>June</t>
@@ -13520,7 +13656,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="19" t="inlineStr">
         <is>
           <t>July</t>
@@ -13555,7 +13691,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="19" t="inlineStr">
         <is>
           <t>August</t>
@@ -13590,7 +13726,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="19" t="inlineStr">
         <is>
           <t>September</t>
@@ -13625,7 +13761,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="19" t="inlineStr">
         <is>
           <t>October</t>
@@ -13660,7 +13796,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="19" t="inlineStr">
         <is>
           <t>November</t>
@@ -13695,7 +13831,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
           <t>December</t>
@@ -13730,7 +13866,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Year</t>
@@ -13765,7 +13901,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Share to savings and debt</t>
@@ -13788,7 +13924,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="H21" s="10">
         <f>IF('Setup'!E24="","",'Setup'!E24)</f>
         <v/>
@@ -13802,7 +13938,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="H22" s="10">
         <f>IF('Setup'!E25="","",'Setup'!E25)</f>
         <v/>
@@ -13840,7 +13976,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Needs</t>
@@ -13863,7 +13999,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Wants</t>
@@ -13886,7 +14022,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Savings</t>
@@ -13909,7 +14045,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Debt</t>
@@ -13932,7 +14068,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="H28" s="10">
         <f>IF('Setup'!E31="","",'Setup'!E31)</f>
         <v/>
@@ -13946,7 +14082,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="H29" s="10">
         <f>IF('Setup'!E32="","",'Setup'!E32)</f>
         <v/>
@@ -13960,7 +14096,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="H30" s="10">
         <f>IF('Setup'!E33="","",'Setup'!E33)</f>
         <v/>
@@ -13974,7 +14110,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="H31" s="10">
         <f>IF('Setup'!E34="","",'Setup'!E34)</f>
         <v/>
@@ -13988,7 +14124,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="H32" s="10">
         <f>IF('Setup'!E35="","",'Setup'!E35)</f>
         <v/>
@@ -14002,7 +14138,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="H33" s="10">
         <f>IF('Setup'!E36="","",'Setup'!E36)</f>
         <v/>
@@ -14016,7 +14152,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="H34" s="10">
         <f>IF('Setup'!E37="","",'Setup'!E37)</f>
         <v/>
@@ -14030,7 +14166,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="H35" s="10">
         <f>IF('Setup'!E38="","",'Setup'!E38)</f>
         <v/>
@@ -14044,7 +14180,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="H36" s="10">
         <f>IF('Setup'!E39="","",'Setup'!E39)</f>
         <v/>
@@ -14208,7 +14344,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Income source</t>
@@ -14659,7 +14795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -14749,7 +14885,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -14785,7 +14921,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n">
         <v>46390</v>
       </c>
@@ -14812,7 +14948,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n">
         <v>46391</v>
       </c>
@@ -14839,7 +14975,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n">
         <v>46393</v>
       </c>
@@ -14866,7 +15002,7 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n">
         <v>46396</v>
       </c>
@@ -14884,7 +15020,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n">
         <v>46398</v>
       </c>
@@ -14928,7 +15064,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n">
         <v>46401</v>
       </c>
@@ -14970,7 +15106,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n">
         <v>46402</v>
       </c>
@@ -15012,7 +15148,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n">
         <v>46405</v>
       </c>
@@ -15054,7 +15190,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n">
         <v>46408</v>
       </c>
@@ -15096,7 +15232,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n">
         <v>46411</v>
       </c>
@@ -15138,7 +15274,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n">
         <v>46412</v>
       </c>
@@ -15180,7 +15316,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -15210,7 +15346,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -15240,7 +15376,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -15270,7 +15406,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -15300,7 +15436,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -15330,7 +15466,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -15360,7 +15496,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -15390,7 +15526,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -15420,7 +15556,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -15450,7 +15586,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -15480,7 +15616,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -15510,7 +15646,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -15540,7 +15676,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -15570,7 +15706,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -15600,7 +15736,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -15630,7 +15766,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -15660,7 +15796,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -15690,7 +15826,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -15720,7 +15856,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -15750,7 +15886,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -15780,7 +15916,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -15810,7 +15946,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -15840,7 +15976,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -15870,7 +16006,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -15900,275 +16036,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -16215,7 +16358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -16305,7 +16448,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -16341,7 +16484,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -16356,7 +16499,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -16371,7 +16514,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -16386,13 +16529,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -16424,7 +16567,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -16454,7 +16597,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -16484,7 +16627,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -16514,7 +16657,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -16544,7 +16687,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -16574,7 +16717,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -16604,7 +16747,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -16634,7 +16777,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -16664,7 +16807,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -16694,7 +16837,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -16724,7 +16867,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -16754,7 +16897,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -16784,7 +16927,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -16814,7 +16957,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -16844,7 +16987,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -16874,7 +17017,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -16904,7 +17047,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -16934,7 +17077,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -16964,7 +17107,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -16994,7 +17137,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -17024,7 +17167,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -17054,7 +17197,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -17084,7 +17227,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -17114,7 +17257,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -17144,7 +17287,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -17174,7 +17317,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -17204,7 +17347,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -17234,7 +17377,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -17264,7 +17407,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -17294,7 +17437,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -17324,275 +17467,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -17639,7 +17789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -17729,7 +17879,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -17765,7 +17915,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -17780,7 +17930,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -17795,7 +17945,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -17810,13 +17960,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -17848,7 +17998,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -17878,7 +18028,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -17908,7 +18058,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -17938,7 +18088,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -17968,7 +18118,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -17998,7 +18148,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -18028,7 +18178,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -18058,7 +18208,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -18088,7 +18238,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -18118,7 +18268,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -18148,7 +18298,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -18178,7 +18328,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -18208,7 +18358,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -18238,7 +18388,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -18268,7 +18418,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -18298,7 +18448,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -18328,7 +18478,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -18358,7 +18508,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -18388,7 +18538,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -18418,7 +18568,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -18448,7 +18598,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -18478,7 +18628,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -18508,7 +18658,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -18538,7 +18688,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -18568,7 +18718,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -18598,7 +18748,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -18628,7 +18778,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -18658,7 +18808,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -18688,7 +18838,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -18718,7 +18868,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -18748,275 +18898,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -19063,7 +19220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -19153,7 +19310,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -19189,7 +19346,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -19204,7 +19361,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -19219,7 +19376,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -19234,13 +19391,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -19272,7 +19429,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -19302,7 +19459,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -19332,7 +19489,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -19362,7 +19519,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -19392,7 +19549,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -19422,7 +19579,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -19452,7 +19609,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -19482,7 +19639,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -19512,7 +19669,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -19542,7 +19699,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -19572,7 +19729,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -19602,7 +19759,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -19632,7 +19789,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -19662,7 +19819,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -19692,7 +19849,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -19722,7 +19879,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -19752,7 +19909,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -19782,7 +19939,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -19812,7 +19969,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -19842,7 +19999,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -19872,7 +20029,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -19902,7 +20059,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -19932,7 +20089,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -19962,7 +20119,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -19992,7 +20149,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -20022,7 +20179,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -20052,7 +20209,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -20082,7 +20239,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -20112,7 +20269,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -20142,7 +20299,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -20172,275 +20329,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -20487,7 +20651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -20577,7 +20741,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -20613,7 +20777,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -20628,7 +20792,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -20643,7 +20807,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -20658,13 +20822,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -20696,7 +20860,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -20726,7 +20890,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -20756,7 +20920,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -20786,7 +20950,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -20816,7 +20980,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -20846,7 +21010,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -20876,7 +21040,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -20906,7 +21070,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -20936,7 +21100,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -20966,7 +21130,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -20996,7 +21160,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -21026,7 +21190,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -21056,7 +21220,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -21086,7 +21250,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -21116,7 +21280,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -21146,7 +21310,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -21176,7 +21340,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -21206,7 +21370,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -21236,7 +21400,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -21266,7 +21430,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -21296,7 +21460,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -21326,7 +21490,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -21356,7 +21520,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -21386,7 +21550,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -21416,7 +21580,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -21446,7 +21610,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -21476,7 +21640,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -21506,7 +21670,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -21536,7 +21700,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -21566,7 +21730,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -21596,275 +21760,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -21911,7 +22082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -22001,7 +22172,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
@@ -22037,7 +22208,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="20" customHeight="1">
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="15" t="n"/>
@@ -22052,7 +22223,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="15" t="n"/>
@@ -22067,7 +22238,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="20" customHeight="1">
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="15" t="n"/>
@@ -22082,13 +22253,13 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="15" t="n"/>
       <c r="E10" s="24" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="15" t="n"/>
@@ -22120,7 +22291,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="15" t="n"/>
@@ -22150,7 +22321,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="15" t="n"/>
@@ -22180,7 +22351,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="15" t="n"/>
@@ -22210,7 +22381,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="20" customHeight="1">
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="15" t="n"/>
@@ -22240,7 +22411,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="15" t="n"/>
@@ -22270,7 +22441,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="20" customHeight="1">
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="15" t="n"/>
@@ -22300,7 +22471,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -22330,7 +22501,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="15" t="n"/>
@@ -22360,7 +22531,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -22390,7 +22561,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="20" customHeight="1">
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="15" t="n"/>
@@ -22420,7 +22591,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="15" t="n"/>
@@ -22450,7 +22621,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="20" customHeight="1">
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -22480,7 +22651,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="15" t="n"/>
@@ -22510,7 +22681,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="20" customHeight="1">
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="15" t="n"/>
@@ -22540,7 +22711,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="20" customHeight="1">
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="15" t="n"/>
@@ -22570,7 +22741,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="20" customHeight="1">
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="15" t="n"/>
@@ -22600,7 +22771,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="20" customHeight="1">
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="15" t="n"/>
@@ -22630,7 +22801,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="20" customHeight="1">
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n"/>
@@ -22660,7 +22831,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="20" customHeight="1">
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="15" t="n"/>
@@ -22690,7 +22861,7 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="20" customHeight="1">
       <c r="B31" s="27" t="n"/>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="15" t="n"/>
@@ -22720,7 +22891,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="B32" s="27" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="15" t="n"/>
@@ -22750,7 +22921,7 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="20" customHeight="1">
       <c r="B33" s="27" t="n"/>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n"/>
@@ -22780,7 +22951,7 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="20" customHeight="1">
       <c r="B34" s="27" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="15" t="n"/>
@@ -22810,7 +22981,7 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="B35" s="27" t="n"/>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n"/>
@@ -22840,7 +23011,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="27" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="15" t="n"/>
@@ -22870,7 +23041,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="20" customHeight="1">
       <c r="B37" s="27" t="n"/>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="15" t="n"/>
@@ -22900,7 +23071,7 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="20" customHeight="1">
       <c r="B38" s="27" t="n"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="15" t="n"/>
@@ -22930,7 +23101,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20" customHeight="1">
       <c r="B39" s="27" t="n"/>
       <c r="C39" s="28" t="n"/>
       <c r="D39" s="15" t="n"/>
@@ -22960,7 +23131,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="B40" s="27" t="n"/>
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="15" t="n"/>
@@ -22990,7 +23161,7 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="20" customHeight="1">
       <c r="B41" s="27" t="n"/>
       <c r="C41" s="28" t="n"/>
       <c r="D41" s="15" t="n"/>
@@ -23020,275 +23191,282 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20" customHeight="1">
       <c r="B42" s="27" t="n"/>
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="24" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="B43" s="27" t="n"/>
       <c r="C43" s="28" t="n"/>
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="24" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="24" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="20" customHeight="1">
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="24" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="B46" s="27" t="n"/>
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="24" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="20" customHeight="1">
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="24" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="B48" s="27" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="24" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="20" customHeight="1">
       <c r="B49" s="27" t="n"/>
       <c r="C49" s="28" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="24" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="B50" s="27" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="24" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="20" customHeight="1">
       <c r="B51" s="27" t="n"/>
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="24" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="B52" s="27" t="n"/>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="24" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="B53" s="27" t="n"/>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="24" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="B54" s="27" t="n"/>
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="24" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="B55" s="27" t="n"/>
       <c r="C55" s="28" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="24" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="B56" s="27" t="n"/>
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="15" t="n"/>
       <c r="E56" s="24" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="20" customHeight="1">
       <c r="B57" s="27" t="n"/>
       <c r="C57" s="28" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="24" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="20" customHeight="1">
       <c r="B58" s="27" t="n"/>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="15" t="n"/>
       <c r="E58" s="24" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="20" customHeight="1">
       <c r="B59" s="27" t="n"/>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="15" t="n"/>
       <c r="E59" s="24" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="B60" s="27" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="15" t="n"/>
       <c r="E60" s="24" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="20" customHeight="1">
       <c r="B61" s="27" t="n"/>
       <c r="C61" s="28" t="n"/>
       <c r="D61" s="15" t="n"/>
       <c r="E61" s="24" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="B62" s="27" t="n"/>
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="24" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="20" customHeight="1">
       <c r="B63" s="27" t="n"/>
       <c r="C63" s="28" t="n"/>
       <c r="D63" s="15" t="n"/>
       <c r="E63" s="24" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="B64" s="27" t="n"/>
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="24" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="20" customHeight="1">
       <c r="B65" s="27" t="n"/>
       <c r="C65" s="28" t="n"/>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="24" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="20" customHeight="1">
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="24" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="B67" s="27" t="n"/>
       <c r="C67" s="28" t="n"/>
       <c r="D67" s="15" t="n"/>
       <c r="E67" s="24" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="B68" s="27" t="n"/>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="24" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="B69" s="27" t="n"/>
       <c r="C69" s="28" t="n"/>
       <c r="D69" s="15" t="n"/>
       <c r="E69" s="24" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="20" customHeight="1">
       <c r="B70" s="27" t="n"/>
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="24" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="20" customHeight="1">
       <c r="B71" s="27" t="n"/>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="24" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="20" customHeight="1">
       <c r="B72" s="27" t="n"/>
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="24" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="20" customHeight="1">
       <c r="B73" s="27" t="n"/>
       <c r="C73" s="28" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="24" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="20" customHeight="1">
       <c r="B74" s="27" t="n"/>
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="15" t="n"/>
       <c r="E74" s="24" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="20" customHeight="1">
       <c r="B75" s="27" t="n"/>
       <c r="C75" s="28" t="n"/>
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="24" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="20" customHeight="1">
       <c r="B76" s="27" t="n"/>
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="15" t="n"/>
       <c r="E76" s="24" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="20" customHeight="1">
       <c r="B77" s="27" t="n"/>
       <c r="C77" s="28" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="24" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="20" customHeight="1">
       <c r="B78" s="27" t="n"/>
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="15" t="n"/>
       <c r="E78" s="24" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="20" customHeight="1">
       <c r="B79" s="27" t="n"/>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="15" t="n"/>
       <c r="E79" s="24" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="20" customHeight="1">
       <c r="B80" s="27" t="n"/>
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="15" t="n"/>
       <c r="E80" s="24" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="20" customHeight="1">
       <c r="B81" s="27" t="n"/>
       <c r="C81" s="28" t="n"/>
       <c r="D81" s="15" t="n"/>
       <c r="E81" s="24" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="20" customHeight="1">
       <c r="B82" s="27" t="n"/>
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="24" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="20" customHeight="1">
       <c r="B83" s="27" t="n"/>
       <c r="C83" s="28" t="n"/>
       <c r="D83" s="15" t="n"/>
       <c r="E83" s="24" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="20" customHeight="1">
       <c r="B84" s="27" t="n"/>
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="15" t="n"/>
       <c r="E84" s="24" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="20" customHeight="1">
       <c r="B85" s="27" t="n"/>
       <c r="C85" s="28" t="n"/>
       <c r="D85" s="15" t="n"/>
       <c r="E85" s="24" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="20" customHeight="1">
       <c r="B86" s="27" t="n"/>
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="15" t="n"/>
       <c r="E86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>

--- a/data/products/p-gsb-001/work/views/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/views/Clear-Budget.xlsx
@@ -10515,7 +10515,7 @@
       <c r="D7" s="24" t="n">
         <v>1400</v>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -10545,7 +10545,7 @@
       <c r="D8" s="24" t="n">
         <v>95</v>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -10575,7 +10575,7 @@
       <c r="D9" s="24" t="n">
         <v>15.99</v>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -10605,7 +10605,7 @@
       <c r="D10" s="24" t="n">
         <v>160</v>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -10635,7 +10635,7 @@
       <c r="D11" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -10665,7 +10665,7 @@
       <c r="D12" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -10687,7 +10687,7 @@
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="23" t="n"/>
       <c r="D13" s="24" t="n"/>
-      <c r="E13" s="15" t="n"/>
+      <c r="E13" s="32" t="n"/>
       <c r="F13" s="32" t="n"/>
       <c r="G13" s="32" t="n"/>
       <c r="H13" s="32" t="n"/>
@@ -10705,7 +10705,7 @@
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="23" t="n"/>
       <c r="D14" s="24" t="n"/>
-      <c r="E14" s="15" t="n"/>
+      <c r="E14" s="32" t="n"/>
       <c r="F14" s="32" t="n"/>
       <c r="G14" s="32" t="n"/>
       <c r="H14" s="32" t="n"/>
@@ -10723,7 +10723,7 @@
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="23" t="n"/>
       <c r="D15" s="24" t="n"/>
-      <c r="E15" s="15" t="n"/>
+      <c r="E15" s="32" t="n"/>
       <c r="F15" s="32" t="n"/>
       <c r="G15" s="32" t="n"/>
       <c r="H15" s="32" t="n"/>
@@ -10741,7 +10741,7 @@
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="23" t="n"/>
       <c r="D16" s="24" t="n"/>
-      <c r="E16" s="15" t="n"/>
+      <c r="E16" s="32" t="n"/>
       <c r="F16" s="32" t="n"/>
       <c r="G16" s="32" t="n"/>
       <c r="H16" s="32" t="n"/>
@@ -10759,7 +10759,7 @@
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="23" t="n"/>
       <c r="D17" s="24" t="n"/>
-      <c r="E17" s="15" t="n"/>
+      <c r="E17" s="32" t="n"/>
       <c r="F17" s="32" t="n"/>
       <c r="G17" s="32" t="n"/>
       <c r="H17" s="32" t="n"/>
@@ -10777,7 +10777,7 @@
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="23" t="n"/>
       <c r="D18" s="24" t="n"/>
-      <c r="E18" s="15" t="n"/>
+      <c r="E18" s="32" t="n"/>
       <c r="F18" s="32" t="n"/>
       <c r="G18" s="32" t="n"/>
       <c r="H18" s="32" t="n"/>
@@ -10795,7 +10795,7 @@
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="23" t="n"/>
       <c r="D19" s="24" t="n"/>
-      <c r="E19" s="15" t="n"/>
+      <c r="E19" s="32" t="n"/>
       <c r="F19" s="32" t="n"/>
       <c r="G19" s="32" t="n"/>
       <c r="H19" s="32" t="n"/>
@@ -10813,7 +10813,7 @@
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="23" t="n"/>
       <c r="D20" s="24" t="n"/>
-      <c r="E20" s="15" t="n"/>
+      <c r="E20" s="32" t="n"/>
       <c r="F20" s="32" t="n"/>
       <c r="G20" s="32" t="n"/>
       <c r="H20" s="32" t="n"/>
@@ -10831,7 +10831,7 @@
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="24" t="n"/>
-      <c r="E21" s="15" t="n"/>
+      <c r="E21" s="32" t="n"/>
       <c r="F21" s="32" t="n"/>
       <c r="G21" s="32" t="n"/>
       <c r="H21" s="32" t="n"/>
@@ -10849,7 +10849,7 @@
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="23" t="n"/>
       <c r="D22" s="24" t="n"/>
-      <c r="E22" s="15" t="n"/>
+      <c r="E22" s="32" t="n"/>
       <c r="F22" s="32" t="n"/>
       <c r="G22" s="32" t="n"/>
       <c r="H22" s="32" t="n"/>
@@ -10867,7 +10867,7 @@
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="24" t="n"/>
-      <c r="E23" s="15" t="n"/>
+      <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
       <c r="G23" s="32" t="n"/>
       <c r="H23" s="32" t="n"/>
@@ -10885,7 +10885,7 @@
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="24" t="n"/>
-      <c r="E24" s="15" t="n"/>
+      <c r="E24" s="32" t="n"/>
       <c r="F24" s="32" t="n"/>
       <c r="G24" s="32" t="n"/>
       <c r="H24" s="32" t="n"/>
@@ -10903,7 +10903,7 @@
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="24" t="n"/>
-      <c r="E25" s="15" t="n"/>
+      <c r="E25" s="32" t="n"/>
       <c r="F25" s="32" t="n"/>
       <c r="G25" s="32" t="n"/>
       <c r="H25" s="32" t="n"/>
@@ -10921,7 +10921,7 @@
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="24" t="n"/>
-      <c r="E26" s="15" t="n"/>
+      <c r="E26" s="32" t="n"/>
       <c r="F26" s="32" t="n"/>
       <c r="G26" s="32" t="n"/>
       <c r="H26" s="32" t="n"/>
@@ -10939,7 +10939,7 @@
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="24" t="n"/>
-      <c r="E27" s="15" t="n"/>
+      <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="32" t="n"/>
       <c r="H27" s="32" t="n"/>
@@ -10957,7 +10957,7 @@
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="24" t="n"/>
-      <c r="E28" s="15" t="n"/>
+      <c r="E28" s="32" t="n"/>
       <c r="F28" s="32" t="n"/>
       <c r="G28" s="32" t="n"/>
       <c r="H28" s="32" t="n"/>
@@ -10975,7 +10975,7 @@
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="24" t="n"/>
-      <c r="E29" s="15" t="n"/>
+      <c r="E29" s="32" t="n"/>
       <c r="F29" s="32" t="n"/>
       <c r="G29" s="32" t="n"/>
       <c r="H29" s="32" t="n"/>
@@ -10993,7 +10993,7 @@
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="24" t="n"/>
-      <c r="E30" s="15" t="n"/>
+      <c r="E30" s="32" t="n"/>
       <c r="F30" s="32" t="n"/>
       <c r="G30" s="32" t="n"/>
       <c r="H30" s="32" t="n"/>
@@ -11011,7 +11011,7 @@
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="15" t="n"/>
+      <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
       <c r="G31" s="32" t="n"/>
       <c r="H31" s="32" t="n"/>
@@ -12615,17 +12615,17 @@
     <row r="10">
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Medical bill</t>
+          <t>Store card</t>
         </is>
       </c>
       <c r="C10" s="24" t="n">
         <v>600</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>0.1999</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F10" s="37">
         <f>IF(C10="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C10,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D10,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12658,7 +12658,7 @@
         <v>2400</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0.2299</v>
+        <v>0.2499</v>
       </c>
       <c r="E11" s="24" t="n">
         <v>75</v>
@@ -13327,7 +13327,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
